--- a/data/hrmas_13C_UMass_cells_012425/results/met_fluxes.xlsx
+++ b/data/hrmas_13C_UMass_cells_012425/results/met_fluxes.xlsx
@@ -534,77 +534,77 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
+          <t>acetate kinase</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
           <t>ATP synthase 4:1</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Butyrate kinase</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>isopentanoylphosphate phosphotransferase</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>acetate kinase</t>
-        </is>
-      </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
+          <t>amino-acid ABC transport (L-threonine)</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>ATP hydrolysis objective</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>ribonucleotide-reductase (ATP)</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>amino-acid ABC transport (L-cysteine)</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>formate:tetrahydrofolate ligase (ADP-forming)</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
           <t>amino-acid ABC transport (glycine)</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>ATP hydrolysis objective</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>amino-acid ABC transport (L-threonine)</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>amino-acid ABC transport (L-cysteine)</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>formate:tetrahydrofolate ligase (ADP-forming)</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>ribonucleotide-reductase (ATP)</t>
-        </is>
-      </c>
       <c r="R2" s="1" t="inlineStr">
         <is>
+          <t>pyruvate formate-lyase_rev</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
           <t>ATP:pyruvate 2-O-phosphotransferase</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>cystathionine gamma-lyase</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t>pyruvate formate-lyase_rev</t>
-        </is>
-      </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
+          <t>dATP:pyruvate 2-O-phosphotransferase</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
           <t>pyruvate:ferredoxin oxidoreductase</t>
-        </is>
-      </c>
-      <c r="V2" s="1" t="inlineStr">
-        <is>
-          <t>dATP:pyruvate 2-O-phosphotransferase</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
@@ -681,77 +681,77 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>ID_280</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>ATPsynth4_1</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>BUK</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>ID_366</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>ID_280</t>
-        </is>
-      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>Trans_thrL</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ATP_sink</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>ID_263</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>Trans_cysL</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>ID_623</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>Trans_gly</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>ATP_sink</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Trans_thrL</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Trans_cysL</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>ID_623</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>ID_263</t>
-        </is>
-      </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
+          <t>ID_36_rev</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
           <t>ID_252</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>ID_469</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>ID_36_rev</t>
-        </is>
-      </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
+          <t>ID_632</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
           <t>ID_53</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>ID_632</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -818,25 +818,25 @@
         <v>0.09029999999999995</v>
       </c>
       <c r="H4" t="n">
+        <v>419.2440289473592</v>
+      </c>
+      <c r="I4" t="n">
         <v>458.1658821052649</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>49.0829615789518</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K4" t="n">
-        <v>419.2440289473592</v>
-      </c>
       <c r="L4" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>-409.2248205263184</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O4" t="n">
         <v>-433.4512863157876</v>
@@ -845,22 +845,22 @@
         <v>-83.72646578947166</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R4" t="n">
+        <v>566.6402136842111</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.09029999999999995</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>433.4512863157876</v>
       </c>
-      <c r="T4" t="n">
-        <v>566.6402136842111</v>
-      </c>
       <c r="U4" t="n">
+        <v>-0.1817999999988079</v>
+      </c>
+      <c r="V4" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.1817999999988079</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -910,25 +910,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H5" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I5" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K5" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L5" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O5" t="n">
         <v>-433.4512863157897</v>
@@ -937,22 +937,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S5" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T5" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U5" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V5" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1002,25 +1002,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H6" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I6" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K6" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L6" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O6" t="n">
         <v>-433.4512863157897</v>
@@ -1029,22 +1029,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S6" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T6" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U6" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V6" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1094,25 +1094,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H7" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I7" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K7" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L7" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O7" t="n">
         <v>-433.4512863157897</v>
@@ -1121,22 +1121,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R7" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S7" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T7" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U7" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V7" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -1186,25 +1186,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H8" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I8" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K8" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L8" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O8" t="n">
         <v>-433.4512863157897</v>
@@ -1213,22 +1213,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R8" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S8" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T8" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U8" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V8" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1278,25 +1278,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H9" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I9" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K9" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L9" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O9" t="n">
         <v>-433.4512863157897</v>
@@ -1305,22 +1305,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R9" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S9" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T9" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U9" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V9" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1370,25 +1370,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H10" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I10" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K10" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L10" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O10" t="n">
         <v>-433.4512863157897</v>
@@ -1397,22 +1397,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R10" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S10" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T10" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U10" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V10" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1462,25 +1462,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H11" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I11" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K11" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L11" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O11" t="n">
         <v>-433.4512863157897</v>
@@ -1489,22 +1489,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R11" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S11" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U11" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V11" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1554,25 +1554,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H12" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I12" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K12" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L12" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O12" t="n">
         <v>-433.4512863157897</v>
@@ -1581,22 +1581,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R12" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S12" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U12" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V12" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1646,25 +1646,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H13" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I13" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K13" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L13" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O13" t="n">
         <v>-433.4512863157897</v>
@@ -1673,22 +1673,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R13" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S13" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U13" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V13" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1738,25 +1738,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H14" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I14" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K14" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L14" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O14" t="n">
         <v>-433.4512863157897</v>
@@ -1765,22 +1765,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R14" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S14" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U14" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V14" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -1830,25 +1830,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H15" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I15" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K15" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L15" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O15" t="n">
         <v>-433.4512863157897</v>
@@ -1857,22 +1857,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R15" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S15" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U15" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V15" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1922,25 +1922,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H16" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I16" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K16" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L16" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O16" t="n">
         <v>-433.4512863157897</v>
@@ -1949,22 +1949,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R16" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S16" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T16" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U16" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V16" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2014,25 +2014,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H17" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I17" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K17" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L17" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O17" t="n">
         <v>-433.4512863157897</v>
@@ -2041,22 +2041,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R17" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S17" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T17" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U17" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V17" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -2106,25 +2106,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H18" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I18" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K18" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L18" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M18" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O18" t="n">
         <v>-433.4512863157897</v>
@@ -2133,22 +2133,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R18" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S18" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T18" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U18" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V18" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -2198,25 +2198,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H19" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I19" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K19" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L19" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O19" t="n">
         <v>-433.4512863157897</v>
@@ -2225,22 +2225,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R19" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S19" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T19" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U19" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V19" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2290,25 +2290,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H20" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I20" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K20" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L20" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O20" t="n">
         <v>-433.4512863157897</v>
@@ -2317,22 +2317,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R20" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S20" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T20" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U20" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V20" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V20" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2382,25 +2382,25 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="H21" t="n">
+        <v>419.2457041035775</v>
+      </c>
+      <c r="I21" t="n">
         <v>458.1652994422337</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>49.08114075698037</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K21" t="n">
-        <v>419.2457041035775</v>
-      </c>
       <c r="L21" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>-409.223291035863</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.179032350609188</v>
       </c>
       <c r="O21" t="n">
         <v>-433.4523059760912</v>
@@ -2409,22 +2409,22 @@
         <v>-83.72901494022804</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.179032350609188</v>
+        <v>-0.0399</v>
       </c>
       <c r="R21" t="n">
+        <v>566.6391940239088</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.09030000000000001</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>433.4523059760912</v>
       </c>
-      <c r="T21" t="n">
-        <v>566.6391940239088</v>
-      </c>
       <c r="U21" t="n">
+        <v>-0.1790323506091801</v>
+      </c>
+      <c r="V21" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.1790323506091801</v>
       </c>
       <c r="W21" t="n">
         <v>-0.002767649390812033</v>
@@ -2474,25 +2474,25 @@
         <v>0.09029999999999996</v>
       </c>
       <c r="H22" t="n">
+        <v>419.2585183645406</v>
+      </c>
+      <c r="I22" t="n">
         <v>458.1608423079858</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>49.06721221245568</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K22" t="n">
-        <v>419.2585183645406</v>
-      </c>
       <c r="L22" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-409.2115910584628</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1578609629322175</v>
       </c>
       <c r="O22" t="n">
         <v>-433.4601059610249</v>
@@ -2501,22 +2501,22 @@
         <v>-83.74851490256232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1578609629322175</v>
+        <v>-0.0399</v>
       </c>
       <c r="R22" t="n">
+        <v>566.631394038975</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.09029999999999996</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>433.4601059610249</v>
       </c>
-      <c r="T22" t="n">
-        <v>566.631394038975</v>
-      </c>
       <c r="U22" t="n">
+        <v>-0.1578609629322333</v>
+      </c>
+      <c r="V22" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-0.1578609629322333</v>
       </c>
       <c r="W22" t="n">
         <v>-0.02393903706778245</v>
@@ -2566,25 +2566,25 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="H23" t="n">
+        <v>419.2696025777178</v>
+      </c>
+      <c r="I23" t="n">
         <v>458.1569869294895</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>49.05516415465439</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K23" t="n">
-        <v>419.2696025777178</v>
-      </c>
       <c r="L23" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-409.2014706899097</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1395479150741367</v>
       </c>
       <c r="O23" t="n">
         <v>-433.4668528733938</v>
@@ -2593,22 +2593,22 @@
         <v>-83.76538218348422</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1395479150741367</v>
+        <v>-0.0399</v>
       </c>
       <c r="R23" t="n">
+        <v>566.6246471266061</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.09030000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>433.4668528733938</v>
       </c>
-      <c r="T23" t="n">
-        <v>566.6246471266061</v>
-      </c>
       <c r="U23" t="n">
+        <v>-0.1395479150741288</v>
+      </c>
+      <c r="V23" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-0.1395479150741288</v>
       </c>
       <c r="W23" t="n">
         <v>-0.04225208492586328</v>
@@ -2658,25 +2658,25 @@
         <v>0.09029999999999996</v>
       </c>
       <c r="H24" t="n">
+        <v>419.2707721234619</v>
+      </c>
+      <c r="I24" t="n">
         <v>458.1565801309695</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>49.05389290928003</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K24" t="n">
-        <v>419.2707721234619</v>
-      </c>
       <c r="L24" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-409.200402843795</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1376156221053495</v>
       </c>
       <c r="O24" t="n">
         <v>-433.467564770803</v>
@@ -2685,22 +2685,22 @@
         <v>-83.76716192700806</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1376156221053495</v>
+        <v>-0.0399</v>
       </c>
       <c r="R24" t="n">
+        <v>566.6239352291969</v>
+      </c>
+      <c r="S24" t="n">
         <v>0.09029999999999996</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>433.467564770803</v>
       </c>
-      <c r="T24" t="n">
-        <v>566.6239352291969</v>
-      </c>
       <c r="U24" t="n">
+        <v>-0.1376156221053692</v>
+      </c>
+      <c r="V24" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-0.1376156221053692</v>
       </c>
       <c r="W24" t="n">
         <v>-0.04418437789465049</v>
@@ -2750,25 +2750,25 @@
         <v>0.09030000000000002</v>
       </c>
       <c r="H25" t="n">
+        <v>419.2667580575407</v>
+      </c>
+      <c r="I25" t="n">
         <v>458.1579763278115</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>49.05825602441128</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K25" t="n">
-        <v>419.2667580575407</v>
-      </c>
       <c r="L25" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-409.2040678605046</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1442475571038212</v>
       </c>
       <c r="O25" t="n">
         <v>-433.4651214263299</v>
@@ -2777,22 +2777,22 @@
         <v>-83.76105356582492</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.1442475571038212</v>
+        <v>-0.0399</v>
       </c>
       <c r="R25" t="n">
+        <v>566.6263785736701</v>
+      </c>
+      <c r="S25" t="n">
         <v>0.09030000000000002</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>433.4651214263299</v>
       </c>
-      <c r="T25" t="n">
-        <v>566.6263785736701</v>
-      </c>
       <c r="U25" t="n">
+        <v>-0.1442475571037778</v>
+      </c>
+      <c r="V25" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-0.1442475571037778</v>
       </c>
       <c r="W25" t="n">
         <v>-0.03755244289617876</v>
@@ -2842,25 +2842,25 @@
         <v>0.09029999999999995</v>
       </c>
       <c r="H26" t="n">
+        <v>419.2664021252549</v>
+      </c>
+      <c r="I26" t="n">
         <v>458.1581001303461</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>49.0586429073316</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K26" t="n">
-        <v>419.2664021252549</v>
-      </c>
       <c r="L26" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-409.2043928421588</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1448356191433368</v>
       </c>
       <c r="O26" t="n">
         <v>-433.4649047718943</v>
@@ -2869,22 +2869,22 @@
         <v>-83.76051192973623</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1448356191433368</v>
+        <v>-0.0399</v>
       </c>
       <c r="R26" t="n">
+        <v>566.6265952281055</v>
+      </c>
+      <c r="S26" t="n">
         <v>0.09029999999999995</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>433.4649047718943</v>
       </c>
-      <c r="T26" t="n">
-        <v>566.6265952281055</v>
-      </c>
       <c r="U26" t="n">
+        <v>-0.1448356191432146</v>
+      </c>
+      <c r="V26" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-0.1448356191432146</v>
       </c>
       <c r="W26" t="n">
         <v>-0.03696438085666312</v>
@@ -2934,25 +2934,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H27" t="n">
+        <v>419.2703561404516</v>
+      </c>
+      <c r="I27" t="n">
         <v>458.1567248207127</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>49.05434506472753</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K27" t="n">
-        <v>419.2703561404516</v>
-      </c>
       <c r="L27" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-409.200782654371</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1383028983870161</v>
       </c>
       <c r="O27" t="n">
         <v>-433.4673115637524</v>
@@ -2961,22 +2961,22 @@
         <v>-83.76652890938068</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.1383028983870161</v>
+        <v>-0.0399</v>
       </c>
       <c r="R27" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6241884362478</v>
       </c>
       <c r="S27" t="n">
+        <v>0.09029999999999998</v>
+      </c>
+      <c r="T27" t="n">
         <v>433.4673115637524</v>
       </c>
-      <c r="T27" t="n">
-        <v>566.6241884362478</v>
-      </c>
       <c r="U27" t="n">
+        <v>-0.1383028983873237</v>
+      </c>
+      <c r="V27" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-0.1383028983873237</v>
       </c>
       <c r="W27" t="n">
         <v>-0.04349710161298392</v>
@@ -3026,25 +3026,25 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="H28" t="n">
+        <v>419.2703119741064</v>
+      </c>
+      <c r="I28" t="n">
         <v>458.1567401829193</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>49.05439307162275</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K28" t="n">
-        <v>419.2703119741064</v>
-      </c>
       <c r="L28" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>-409.2008229801629</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1383758688651809</v>
       </c>
       <c r="O28" t="n">
         <v>-433.4672846798917</v>
@@ -3053,22 +3053,22 @@
         <v>-83.76646169972904</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.1383758688651809</v>
+        <v>-0.0399</v>
       </c>
       <c r="R28" t="n">
+        <v>566.6242153201081</v>
+      </c>
+      <c r="S28" t="n">
         <v>0.09030000000000001</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>433.4672846798917</v>
       </c>
-      <c r="T28" t="n">
-        <v>566.6242153201081</v>
-      </c>
       <c r="U28" t="n">
+        <v>-0.138375868865031</v>
+      </c>
+      <c r="V28" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V28" t="n">
-        <v>-0.138375868865031</v>
       </c>
       <c r="W28" t="n">
         <v>-0.04342413113481911</v>
@@ -3118,25 +3118,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H29" t="n">
+        <v>419.260180511032</v>
+      </c>
+      <c r="I29" t="n">
         <v>458.1602641700759</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>49.06540553148749</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K29" t="n">
-        <v>419.260180511032</v>
-      </c>
       <c r="L29" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>-409.2100734464493</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1551148078616329</v>
       </c>
       <c r="O29" t="n">
         <v>-433.461117702367</v>
@@ -3145,22 +3145,22 @@
         <v>-83.75104425591714</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.1551148078616329</v>
+        <v>-0.0399</v>
       </c>
       <c r="R29" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6303822976331</v>
       </c>
       <c r="S29" t="n">
+        <v>0.09029999999999998</v>
+      </c>
+      <c r="T29" t="n">
         <v>433.461117702367</v>
       </c>
-      <c r="T29" t="n">
-        <v>566.6303822976331</v>
-      </c>
       <c r="U29" t="n">
+        <v>-0.155114807861905</v>
+      </c>
+      <c r="V29" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V29" t="n">
-        <v>-0.155114807861905</v>
       </c>
       <c r="W29" t="n">
         <v>-0.02668519213836711</v>
@@ -3210,25 +3210,25 @@
         <v>0.09029999999999995</v>
       </c>
       <c r="H30" t="n">
+        <v>419.2470446286342</v>
+      </c>
+      <c r="I30" t="n">
         <v>458.1648331726491</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>49.07968366452885</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K30" t="n">
-        <v>419.2470446286342</v>
-      </c>
       <c r="L30" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>-409.2220670782044</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1768175700844644</v>
       </c>
       <c r="O30" t="n">
         <v>-433.4531219478638</v>
@@ -3237,22 +3237,22 @@
         <v>-83.73105486965926</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.1768175700844644</v>
+        <v>-0.0399</v>
       </c>
       <c r="R30" t="n">
+        <v>566.6383780521363</v>
+      </c>
+      <c r="S30" t="n">
         <v>0.09029999999999995</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>433.4531219478638</v>
       </c>
-      <c r="T30" t="n">
-        <v>566.6383780521363</v>
-      </c>
       <c r="U30" t="n">
+        <v>-0.1768175700845473</v>
+      </c>
+      <c r="V30" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V30" t="n">
-        <v>-0.1768175700845473</v>
       </c>
       <c r="W30" t="n">
         <v>-0.004982429915535518</v>
@@ -3302,25 +3302,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H31" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I31" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K31" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L31" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M31" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O31" t="n">
         <v>-433.4512863157897</v>
@@ -3329,22 +3329,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R31" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S31" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T31" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U31" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V31" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V31" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -3394,25 +3394,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H32" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I32" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K32" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L32" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M32" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O32" t="n">
         <v>-433.4512863157897</v>
@@ -3421,22 +3421,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R32" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S32" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T32" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U32" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V32" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V32" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3486,25 +3486,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H33" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I33" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K33" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L33" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M33" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O33" t="n">
         <v>-433.4512863157897</v>
@@ -3513,22 +3513,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R33" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S33" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T33" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U33" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V33" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V33" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -3578,25 +3578,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H34" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I34" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K34" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L34" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M34" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O34" t="n">
         <v>-433.4512863157897</v>
@@ -3605,22 +3605,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R34" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S34" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T34" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U34" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V34" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V34" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3670,25 +3670,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H35" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I35" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K35" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L35" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O35" t="n">
         <v>-433.4512863157897</v>
@@ -3697,22 +3697,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R35" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S35" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T35" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U35" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V35" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V35" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -3762,25 +3762,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H36" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I36" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K36" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L36" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M36" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O36" t="n">
         <v>-433.4512863157897</v>
@@ -3789,22 +3789,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R36" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S36" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T36" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U36" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V36" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V36" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3854,25 +3854,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H37" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I37" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K37" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L37" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O37" t="n">
         <v>-433.4512863157897</v>
@@ -3881,22 +3881,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R37" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S37" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T37" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U37" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V37" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V37" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3946,25 +3946,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H38" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I38" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K38" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L38" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O38" t="n">
         <v>-433.4512863157897</v>
@@ -3973,22 +3973,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R38" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S38" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T38" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U38" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V38" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V38" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -4038,25 +4038,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H39" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I39" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K39" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L39" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O39" t="n">
         <v>-433.4512863157897</v>
@@ -4065,22 +4065,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R39" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S39" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T39" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U39" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V39" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V39" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4130,25 +4130,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H40" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I40" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K40" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L40" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M40" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O40" t="n">
         <v>-433.4512863157897</v>
@@ -4157,22 +4157,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R40" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S40" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T40" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U40" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V40" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V40" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4222,25 +4222,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H41" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I41" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K41" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L41" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O41" t="n">
         <v>-433.4512863157897</v>
@@ -4249,22 +4249,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R41" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S41" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T41" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U41" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V41" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V41" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -4314,25 +4314,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H42" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I42" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K42" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L42" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O42" t="n">
         <v>-433.4512863157897</v>
@@ -4341,22 +4341,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R42" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S42" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T42" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U42" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V42" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V42" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -4406,25 +4406,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H43" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I43" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K43" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L43" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M43" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O43" t="n">
         <v>-433.4512863157897</v>
@@ -4433,22 +4433,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R43" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S43" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T43" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U43" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V43" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V43" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4498,25 +4498,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H44" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I44" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K44" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L44" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M44" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O44" t="n">
         <v>-433.4512863157897</v>
@@ -4525,22 +4525,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R44" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S44" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T44" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U44" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V44" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V44" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4590,25 +4590,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H45" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I45" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K45" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L45" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O45" t="n">
         <v>-433.4512863157897</v>
@@ -4617,22 +4617,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R45" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S45" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T45" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U45" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V45" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V45" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -4682,25 +4682,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H46" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I46" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K46" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L46" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M46" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O46" t="n">
         <v>-433.4512863157897</v>
@@ -4709,22 +4709,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R46" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S46" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T46" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U46" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V46" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V46" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -4774,25 +4774,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H47" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I47" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K47" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L47" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O47" t="n">
         <v>-433.4512863157897</v>
@@ -4801,22 +4801,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R47" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S47" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T47" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U47" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V47" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V47" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -4866,25 +4866,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H48" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I48" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K48" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L48" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M48" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O48" t="n">
         <v>-433.4512863157897</v>
@@ -4893,22 +4893,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R48" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S48" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T48" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U48" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V48" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V48" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -4958,25 +4958,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H49" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I49" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K49" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L49" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M49" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O49" t="n">
         <v>-433.4512863157897</v>
@@ -4985,22 +4985,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R49" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S49" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T49" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U49" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V49" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V49" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -5050,25 +5050,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H50" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I50" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K50" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L50" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O50" t="n">
         <v>-433.4512863157897</v>
@@ -5077,22 +5077,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R50" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S50" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T50" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U50" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V50" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V50" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5142,25 +5142,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H51" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I51" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K51" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L51" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M51" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O51" t="n">
         <v>-433.4512863157897</v>
@@ -5169,22 +5169,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R51" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S51" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T51" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U51" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V51" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V51" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5234,25 +5234,25 @@
         <v>0.09029999999999998</v>
       </c>
       <c r="H52" t="n">
+        <v>419.2440289473698</v>
+      </c>
+      <c r="I52" t="n">
         <v>458.1658821052629</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>49.0829615789468</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>0.09149999999999998</v>
       </c>
-      <c r="K52" t="n">
-        <v>419.2440289473698</v>
-      </c>
       <c r="L52" t="n">
-        <v>-0.0399</v>
+        <v>-0.05039999999999999</v>
       </c>
       <c r="M52" t="n">
         <v>-409.2248205263156</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.05039999999999999</v>
+        <v>-0.1818</v>
       </c>
       <c r="O52" t="n">
         <v>-433.4512863157897</v>
@@ -5261,22 +5261,22 @@
         <v>-83.72646578947399</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.1818</v>
+        <v>-0.0399</v>
       </c>
       <c r="R52" t="n">
-        <v>0.09029999999999998</v>
+        <v>566.6402136842105</v>
       </c>
       <c r="S52" t="n">
-        <v>433.4512863157897</v>
+        <v>0.09029999999999998</v>
       </c>
       <c r="T52" t="n">
-        <v>566.6402136842105</v>
+        <v>433.4512863157897</v>
       </c>
       <c r="U52" t="n">
+        <v>-0.1818000000002248</v>
+      </c>
+      <c r="V52" t="n">
         <v>-1000</v>
-      </c>
-      <c r="V52" t="n">
-        <v>-0.1818000000002248</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>

--- a/data/hrmas_13C_UMass_cells_012425/results/met_fluxes.xlsx
+++ b/data/hrmas_13C_UMass_cells_012425/results/met_fluxes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:Z52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,57 +445,52 @@
           <t>L-glutamate influx</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>L-glutamate outflux</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ATP influx</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ATP outflux</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>pyruvate influx</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pyruvate outflux</t>
+        </is>
+      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>pyruvate outflux</t>
+          <t>ammonia influx</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ammonia outflux</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>ammonia influx</t>
+          <t>dATP influx</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dATP outflux</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ammonia outflux</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dATP influx</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dATP outflux</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>L-cysteine influx</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>L-cysteine outflux</t>
         </is>
@@ -514,137 +509,112 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
+          <t>isoleucine dehydrogenase_rev</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
           <t>L-Leucine:2-oxoglutarate aminotransferase_rev</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>3-phospho-L-serinephosphoserine transaminase</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>L-glutamate:NAD+ oxidoreductase (deaminating)</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>L-alanine:2-oxoglutarate aminotransferase_rev</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>ATP:pyruvate 2-O-phosphotransferase</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>acetate kinase</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>2-methylbutanoyl phosphate transferase</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>ATP synthase 4:1</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>Butyrate kinase</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>isopentanoylphosphate phosphotransferase</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>ATP hydrolysis objective</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>amino-acid ABC transport (L-threonine)</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>ATP hydrolysis objective</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>ribonucleotide-reductase (ATP)</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>amino-acid ABC transport (L-cysteine)</t>
-        </is>
-      </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>formate:tetrahydrofolate ligase (ADP-forming)</t>
+          <t>pyruvate formate-lyase_rev</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>amino-acid ABC transport (glycine)</t>
+          <t>2-acetolactate pyruvate-lyase (carboxylating)</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>pyruvate formate-lyase_rev</t>
+          <t>dATP:pyruvate 2-O-phosphotransferase</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>ATP:pyruvate 2-O-phosphotransferase</t>
+          <t>pyruvate:ferredoxin oxidoreductase</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>cystathionine gamma-lyase</t>
+          <t>L-alanine:2-oxoglutarate aminotransferase_rev</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
+          <t>glycine reductase</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>L-glutamate:NAD+ oxidoreductase (deaminating)</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>ammonia transport_rev</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="inlineStr">
+        <is>
+          <t>ribonucleotide-reductase (ATP)</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>dATP:pyruvate 2-O-phosphotransferase</t>
-        </is>
-      </c>
-      <c r="V2" s="1" t="inlineStr">
-        <is>
-          <t>pyruvate:ferredoxin oxidoreductase</t>
-        </is>
-      </c>
-      <c r="W2" s="1" t="inlineStr">
-        <is>
-          <t>L-alanine:2-oxoglutarate aminotransferase_rev</t>
-        </is>
-      </c>
-      <c r="X2" s="1" t="inlineStr">
-        <is>
-          <t>glycine reductase</t>
-        </is>
-      </c>
-      <c r="Y2" s="1" t="inlineStr">
-        <is>
-          <t>cystathionine gamma-lyase</t>
-        </is>
-      </c>
-      <c r="Z2" s="1" t="inlineStr">
-        <is>
-          <t>ammonia transport_rev</t>
-        </is>
-      </c>
-      <c r="AA2" s="1" t="inlineStr">
-        <is>
-          <t>ribonucleotide-reductase (ATP)</t>
-        </is>
-      </c>
-      <c r="AB2" s="1" t="inlineStr">
-        <is>
-          <t>dATP:pyruvate 2-O-phosphotransferase</t>
-        </is>
-      </c>
-      <c r="AC2" s="1" t="inlineStr">
-        <is>
-          <t>amino-acid ABC transport (L-cysteine)</t>
-        </is>
-      </c>
-      <c r="AD2" s="1" t="inlineStr">
-        <is>
-          <t>cystathionine gamma-lyase</t>
         </is>
       </c>
     </row>
@@ -661,137 +631,112 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>ID_709_rev</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>ID_28_rev</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>ID_665</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ID_575</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>ID_336_rev</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>ID_252</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>ID_280</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ID_146</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>ATPsynth4_1</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>BUK</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>ID_366</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ATP_sink</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Trans_thrL</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>ATP_sink</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>ID_263</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Trans_cysL</t>
-        </is>
-      </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>ID_623</t>
+          <t>ID_36_rev</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Trans_gly</t>
+          <t>ID_449</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>ID_36_rev</t>
+          <t>ID_632</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>ID_252</t>
+          <t>ID_53</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>ID_469</t>
+          <t>ID_336_rev</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
+          <t>ID_603</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>ID_575</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Trans_nh_rev</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>ID_263</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
           <t>ID_632</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>ID_53</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>ID_336_rev</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>ID_603</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>ID_469</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>Trans_nh_rev</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>ID_263</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>ID_632</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>Trans_cysL</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>ID_469</t>
         </is>
       </c>
     </row>
@@ -806,85 +751,70 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0915</v>
+        <v>2.29000000000011</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0915</v>
+        <v>3.049999999999841</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-2.669999999999965</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09029999999999995</v>
+        <v>-2.669999999999777</v>
       </c>
       <c r="H4" t="n">
-        <v>419.2440289473592</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>458.1658821052649</v>
+        <v>6.029999999999455</v>
       </c>
       <c r="J4" t="n">
-        <v>49.0829615789518</v>
+        <v>2.29000000000011</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.4800000000014</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.049999999999841</v>
       </c>
       <c r="M4" t="n">
-        <v>-409.2248205263184</v>
+        <v>-59.50000000000032</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O4" t="n">
-        <v>-433.4512863157876</v>
+        <v>-2.669999999999788</v>
       </c>
       <c r="P4" t="n">
-        <v>-83.72646578947166</v>
+        <v>206.5600000000048</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0399</v>
+        <v>-2.669999999999407</v>
       </c>
       <c r="R4" t="n">
-        <v>566.6402136842111</v>
+        <v>-2.669999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09029999999999995</v>
+        <v>-201.2200000000055</v>
       </c>
       <c r="T4" t="n">
-        <v>433.4512863157876</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1817999999988079</v>
+        <v>4.349999999999968</v>
       </c>
       <c r="V4" t="n">
-        <v>-1000</v>
+        <v>2.669999999999777</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-7.019999999999368</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999788</v>
       </c>
       <c r="Y4" t="n">
-        <v>433.4512863157876</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-433.6330863157887</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.1817999999988079</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>433.4512863157876</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-433.4512863157876</v>
+        <v>-2.669999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -898,85 +828,70 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H5" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J5" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O5" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P5" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R5" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T5" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V5" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y5" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="6">
@@ -990,85 +905,70 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H6" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J6" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O6" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P6" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R6" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T6" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V6" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y6" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="7">
@@ -1082,85 +982,70 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H7" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J7" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M7" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O7" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P7" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R7" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T7" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V7" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y7" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="8">
@@ -1174,85 +1059,70 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H8" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J8" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O8" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P8" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R8" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T8" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V8" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y8" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="9">
@@ -1266,85 +1136,70 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H9" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J9" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M9" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O9" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P9" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R9" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T9" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V9" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y9" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="10">
@@ -1358,85 +1213,70 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J10" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M10" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O10" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P10" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R10" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T10" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V10" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y10" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="11">
@@ -1450,85 +1290,70 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H11" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J11" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O11" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P11" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R11" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V11" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y11" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="12">
@@ -1542,85 +1367,70 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H12" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J12" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O12" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P12" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R12" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V12" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y12" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="13">
@@ -1634,85 +1444,70 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H13" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J13" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K13" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M13" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O13" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P13" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R13" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T13" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V13" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y13" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="14">
@@ -1726,85 +1521,70 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G14" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H14" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J14" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P14" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R14" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S14" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T14" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V14" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y14" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="15">
@@ -1818,85 +1598,70 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H15" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J15" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M15" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O15" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P15" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R15" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S15" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T15" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V15" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y15" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="16">
@@ -1910,85 +1675,70 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H16" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J16" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M16" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O16" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P16" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R16" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V16" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y16" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="17">
@@ -2002,85 +1752,70 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H17" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J17" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K17" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O17" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P17" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R17" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S17" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T17" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V17" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y17" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="18">
@@ -2094,85 +1829,70 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H18" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J18" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K18" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O18" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P18" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R18" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S18" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T18" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V18" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y18" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="19">
@@ -2186,85 +1906,70 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H19" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J19" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O19" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P19" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R19" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S19" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T19" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V19" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y19" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="20">
@@ -2278,85 +1983,70 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H20" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J20" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K20" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O20" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P20" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R20" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T20" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V20" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y20" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="21">
@@ -2364,91 +2054,76 @@
         <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>0.002767649390812033</v>
+        <v>0.00276764939081048</v>
       </c>
       <c r="C21" t="n">
         <v>-0.002767649390812032</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.08873235060918798</v>
+        <v>3.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.002767649390812033</v>
+        <v>-2.668616175304598</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09030000000000001</v>
+        <v>-2.668616175304589</v>
       </c>
       <c r="H21" t="n">
-        <v>419.2457041035775</v>
+        <v>-0.00276764939081048</v>
       </c>
       <c r="I21" t="n">
-        <v>458.1652994422337</v>
+        <v>6.025848525913741</v>
       </c>
       <c r="J21" t="n">
-        <v>49.08114075698037</v>
+        <v>2.29</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.48276764939072</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M21" t="n">
-        <v>-409.223291035863</v>
+        <v>-59.49999999999994</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.179032350609188</v>
+        <v>-1.68</v>
       </c>
       <c r="O21" t="n">
-        <v>-433.4523059760912</v>
+        <v>-2.668616175304535</v>
       </c>
       <c r="P21" t="n">
-        <v>-83.72901494022804</v>
+        <v>206.5710705975632</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.0399</v>
+        <v>-2.668616175304761</v>
       </c>
       <c r="R21" t="n">
-        <v>566.6391940239088</v>
+        <v>-2.668616175304535</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09030000000000001</v>
+        <v>-201.231070597563</v>
       </c>
       <c r="T21" t="n">
-        <v>433.4523059760912</v>
+        <v>-0.00276764939081048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1790323506091801</v>
+        <v>4.348616175304599</v>
       </c>
       <c r="V21" t="n">
-        <v>-1000</v>
+        <v>2.668616175304589</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.002767649390812033</v>
+        <v>-7.017232350609222</v>
       </c>
       <c r="X21" t="n">
-        <v>0.179032350609188</v>
+        <v>2.668616175304535</v>
       </c>
       <c r="Y21" t="n">
-        <v>433.4523059760912</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>-433.6313383267006</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.179032350609188</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>-0.1790323506091801</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>433.4523059760912</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>-433.4523059760912</v>
+        <v>-2.668616175304535</v>
       </c>
     </row>
     <row r="22">
@@ -2456,91 +2131,76 @@
         <v>18</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02393903706778245</v>
+        <v>0.02393903706778167</v>
       </c>
       <c r="C22" t="n">
         <v>-0.02393903706778245</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.06756096293221754</v>
+        <v>3.05</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.02393903706778245</v>
+        <v>-2.6580304814661</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09029999999999996</v>
+        <v>-2.658030481466116</v>
       </c>
       <c r="H22" t="n">
-        <v>419.2585183645406</v>
+        <v>-0.02393903706778167</v>
       </c>
       <c r="I22" t="n">
-        <v>458.1608423079858</v>
+        <v>5.994091444398274</v>
       </c>
       <c r="J22" t="n">
-        <v>49.06721221245568</v>
+        <v>2.29</v>
       </c>
       <c r="K22" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.50393903706767</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M22" t="n">
-        <v>-409.2115910584628</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1578609629322175</v>
+        <v>-1.68</v>
       </c>
       <c r="O22" t="n">
-        <v>-433.4601059610249</v>
+        <v>-2.658030481466028</v>
       </c>
       <c r="P22" t="n">
-        <v>-83.74851490256232</v>
+        <v>206.655756148271</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0399</v>
+        <v>-2.658030481466255</v>
       </c>
       <c r="R22" t="n">
-        <v>566.631394038975</v>
+        <v>-2.658030481466028</v>
       </c>
       <c r="S22" t="n">
-        <v>0.09029999999999996</v>
+        <v>-201.3157561482709</v>
       </c>
       <c r="T22" t="n">
-        <v>433.4601059610249</v>
+        <v>-0.02393903706778167</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1578609629322333</v>
+        <v>4.338030481466099</v>
       </c>
       <c r="V22" t="n">
-        <v>-1000</v>
+        <v>2.658030481466116</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.02393903706778245</v>
+        <v>-6.996060962932252</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1578609629322175</v>
+        <v>2.658030481466028</v>
       </c>
       <c r="Y22" t="n">
-        <v>433.4601059610249</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-433.6179669239573</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.1578609629322175</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-0.1578609629322333</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>433.4601059610249</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>-433.4601059610249</v>
+        <v>-2.658030481466028</v>
       </c>
     </row>
     <row r="23">
@@ -2548,91 +2208,76 @@
         <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>0.04225208492586328</v>
+        <v>0.04225208492586249</v>
       </c>
       <c r="C23" t="n">
         <v>-0.04225208492586327</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.04924791507413671</v>
+        <v>3.05</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.04225208492586328</v>
+        <v>-2.648873957537064</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09030000000000001</v>
+        <v>-2.648873957537071</v>
       </c>
       <c r="H23" t="n">
-        <v>419.2696025777178</v>
+        <v>-0.04225208492586249</v>
       </c>
       <c r="I23" t="n">
-        <v>458.1569869294895</v>
+        <v>5.966621872611158</v>
       </c>
       <c r="J23" t="n">
-        <v>49.05516415465439</v>
+        <v>2.29</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.52225208492577</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M23" t="n">
-        <v>-409.2014706899097</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1395479150741367</v>
+        <v>-1.68</v>
       </c>
       <c r="O23" t="n">
-        <v>-433.4668528733938</v>
+        <v>-2.648873957536984</v>
       </c>
       <c r="P23" t="n">
-        <v>-83.76538218348422</v>
+        <v>206.7290083397033</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.0399</v>
+        <v>-2.648873957537186</v>
       </c>
       <c r="R23" t="n">
-        <v>566.6246471266061</v>
+        <v>-2.648873957536985</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09030000000000001</v>
+        <v>-201.3890083397031</v>
       </c>
       <c r="T23" t="n">
-        <v>433.4668528733938</v>
+        <v>-0.04225208492586249</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1395479150741288</v>
+        <v>4.328873957537064</v>
       </c>
       <c r="V23" t="n">
-        <v>-1000</v>
+        <v>2.648873957537071</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.04225208492586328</v>
+        <v>-6.977747915074175</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1395479150741367</v>
+        <v>2.648873957536984</v>
       </c>
       <c r="Y23" t="n">
-        <v>433.4668528733938</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-433.6064007884681</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.1395479150741367</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.1395479150741288</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>433.4668528733938</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>-433.4668528733938</v>
+        <v>-2.648873957536985</v>
       </c>
     </row>
     <row r="24">
@@ -2646,85 +2291,70 @@
         <v>-0.04418437789465049</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.04731562210534949</v>
+        <v>3.05</v>
       </c>
       <c r="F24" t="n">
+        <v>-2.647907811052678</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.647907811052669</v>
+      </c>
+      <c r="H24" t="n">
         <v>-0.04418437789465049</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.09029999999999996</v>
-      </c>
-      <c r="H24" t="n">
-        <v>419.2707721234619</v>
-      </c>
       <c r="I24" t="n">
-        <v>458.1565801309695</v>
+        <v>5.963723433157985</v>
       </c>
       <c r="J24" t="n">
-        <v>49.05389290928003</v>
+        <v>2.29</v>
       </c>
       <c r="K24" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.52418437789456</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M24" t="n">
-        <v>-409.200402843795</v>
+        <v>-59.49999999999993</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1376156221053495</v>
+        <v>-1.68</v>
       </c>
       <c r="O24" t="n">
-        <v>-433.467564770803</v>
+        <v>-2.647907811052591</v>
       </c>
       <c r="P24" t="n">
-        <v>-83.76716192700806</v>
+        <v>206.7367375115785</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.0399</v>
+        <v>-2.647907811052847</v>
       </c>
       <c r="R24" t="n">
-        <v>566.6239352291969</v>
+        <v>-2.647907811052591</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09029999999999996</v>
+        <v>-201.3967375115784</v>
       </c>
       <c r="T24" t="n">
-        <v>433.467564770803</v>
+        <v>-0.04418437789465049</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1376156221053692</v>
+        <v>4.327907811052678</v>
       </c>
       <c r="V24" t="n">
-        <v>-1000</v>
+        <v>2.647907811052669</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.04418437789465049</v>
+        <v>-6.975815622105391</v>
       </c>
       <c r="X24" t="n">
-        <v>0.1376156221053495</v>
+        <v>2.647907811052591</v>
       </c>
       <c r="Y24" t="n">
-        <v>433.467564770803</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-433.6051803929084</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.1376156221053495</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>-0.1376156221053692</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>433.467564770803</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-433.467564770803</v>
+        <v>-2.647907811052591</v>
       </c>
     </row>
     <row r="25">
@@ -2732,91 +2362,76 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03755244289617876</v>
+        <v>0.03755244289617798</v>
       </c>
       <c r="C25" t="n">
         <v>-0.03755244289617876</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.05394755710382122</v>
+        <v>3.05</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.03755244289617876</v>
+        <v>-2.651223778551912</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09030000000000002</v>
+        <v>-2.651223778551908</v>
       </c>
       <c r="H25" t="n">
-        <v>419.2667580575407</v>
+        <v>-0.03755244289617798</v>
       </c>
       <c r="I25" t="n">
-        <v>458.1579763278115</v>
+        <v>5.973671335655689</v>
       </c>
       <c r="J25" t="n">
-        <v>49.05825602441128</v>
+        <v>2.29</v>
       </c>
       <c r="K25" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.51755244289605</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M25" t="n">
-        <v>-409.2040678605046</v>
+        <v>-59.49999999999993</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1442475571038212</v>
+        <v>-1.68</v>
       </c>
       <c r="O25" t="n">
-        <v>-433.4651214263299</v>
+        <v>-2.651223778551825</v>
       </c>
       <c r="P25" t="n">
-        <v>-83.76105356582492</v>
+        <v>206.7102097715845</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.0399</v>
+        <v>-2.651223778552095</v>
       </c>
       <c r="R25" t="n">
-        <v>566.6263785736701</v>
+        <v>-2.651223778551825</v>
       </c>
       <c r="S25" t="n">
-        <v>0.09030000000000002</v>
+        <v>-201.3702097715843</v>
       </c>
       <c r="T25" t="n">
-        <v>433.4651214263299</v>
+        <v>-0.03755244289617798</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1442475571037778</v>
+        <v>4.331223778551911</v>
       </c>
       <c r="V25" t="n">
-        <v>-1000</v>
+        <v>2.651223778551908</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.03755244289617876</v>
+        <v>-6.982447557103864</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1442475571038212</v>
+        <v>2.651223778551825</v>
       </c>
       <c r="Y25" t="n">
-        <v>433.4651214263299</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-433.6093689834339</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.1442475571038212</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-0.1442475571037778</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>433.4651214263299</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-433.4651214263299</v>
+        <v>-2.651223778551825</v>
       </c>
     </row>
     <row r="26">
@@ -2824,91 +2439,76 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03696438085666312</v>
+        <v>0.03696438085666234</v>
       </c>
       <c r="C26" t="n">
         <v>-0.03696438085666311</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.05453561914333688</v>
+        <v>3.05</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.03696438085666312</v>
+        <v>-2.651517809571661</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09029999999999995</v>
+        <v>-2.651517809571675</v>
       </c>
       <c r="H26" t="n">
-        <v>419.2664021252549</v>
+        <v>-0.03696438085666234</v>
       </c>
       <c r="I26" t="n">
-        <v>458.1581001303461</v>
+        <v>5.974553428714954</v>
       </c>
       <c r="J26" t="n">
-        <v>49.0586429073316</v>
+        <v>2.29</v>
       </c>
       <c r="K26" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.51696438085656</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M26" t="n">
-        <v>-409.2043928421588</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1448356191433368</v>
+        <v>-1.68</v>
       </c>
       <c r="O26" t="n">
-        <v>-433.4649047718943</v>
+        <v>-2.651517809571589</v>
       </c>
       <c r="P26" t="n">
-        <v>-83.76051192973623</v>
+        <v>206.7078575234266</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.0399</v>
+        <v>-2.651517809571816</v>
       </c>
       <c r="R26" t="n">
-        <v>566.6265952281055</v>
+        <v>-2.651517809571589</v>
       </c>
       <c r="S26" t="n">
-        <v>0.09029999999999995</v>
+        <v>-201.3678575234264</v>
       </c>
       <c r="T26" t="n">
-        <v>433.4649047718943</v>
+        <v>-0.03696438085666234</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1448356191432146</v>
+        <v>4.331517809571661</v>
       </c>
       <c r="V26" t="n">
-        <v>-1000</v>
+        <v>2.651517809571675</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.03696438085666312</v>
+        <v>-6.983035619143373</v>
       </c>
       <c r="X26" t="n">
-        <v>0.1448356191433369</v>
+        <v>2.651517809571589</v>
       </c>
       <c r="Y26" t="n">
-        <v>433.4649047718943</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>-433.6097403910379</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.1448356191433368</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>-0.1448356191432146</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>433.4649047718943</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>-433.4649047718943</v>
+        <v>-2.651517809571589</v>
       </c>
     </row>
     <row r="27">
@@ -2916,91 +2516,76 @@
         <v>23</v>
       </c>
       <c r="B27" t="n">
-        <v>0.04349710161298392</v>
+        <v>0.04349710161298314</v>
       </c>
       <c r="C27" t="n">
         <v>-0.04349710161298392</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.04800289838701607</v>
+        <v>3.05</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.04349710161298392</v>
+        <v>-2.648251449193516</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.648251449193499</v>
       </c>
       <c r="H27" t="n">
-        <v>419.2703561404516</v>
+        <v>-0.04349710161298314</v>
       </c>
       <c r="I27" t="n">
-        <v>458.1567248207127</v>
+        <v>5.964754347580488</v>
       </c>
       <c r="J27" t="n">
-        <v>49.05434506472753</v>
+        <v>2.29</v>
       </c>
       <c r="K27" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.5234971016129</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M27" t="n">
-        <v>-409.200782654371</v>
+        <v>-59.49999999999994</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1383028983870161</v>
+        <v>-1.68</v>
       </c>
       <c r="O27" t="n">
-        <v>-433.4673115637524</v>
+        <v>-2.648251449193436</v>
       </c>
       <c r="P27" t="n">
-        <v>-83.76652890938068</v>
+        <v>206.7339884064518</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.0399</v>
+        <v>-2.648251449193657</v>
       </c>
       <c r="R27" t="n">
-        <v>566.6241884362478</v>
+        <v>-2.648251449193436</v>
       </c>
       <c r="S27" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.3939884064517</v>
       </c>
       <c r="T27" t="n">
-        <v>433.4673115637524</v>
+        <v>-0.04349710161298314</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1383028983873237</v>
+        <v>4.328251449193516</v>
       </c>
       <c r="V27" t="n">
-        <v>-1000</v>
+        <v>2.648251449193499</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.04349710161298392</v>
+        <v>-6.976502898387056</v>
       </c>
       <c r="X27" t="n">
-        <v>0.1383028983870161</v>
+        <v>2.648251449193436</v>
       </c>
       <c r="Y27" t="n">
-        <v>433.4673115637524</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>-433.6056144621393</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.1383028983870161</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>-0.1383028983873237</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>433.4673115637524</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>-433.4673115637524</v>
+        <v>-2.648251449193436</v>
       </c>
     </row>
     <row r="28">
@@ -3008,91 +2593,76 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04342413113481911</v>
+        <v>0.0434241311348191</v>
       </c>
       <c r="C28" t="n">
         <v>-0.0434241311348191</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.04807586886518089</v>
+        <v>3.05</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.04342413113481911</v>
+        <v>-2.64828793443258</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09030000000000001</v>
+        <v>-2.6482879344326</v>
       </c>
       <c r="H28" t="n">
-        <v>419.2703119741064</v>
+        <v>-0.0434241311348191</v>
       </c>
       <c r="I28" t="n">
-        <v>458.1567401829193</v>
+        <v>5.964863803297717</v>
       </c>
       <c r="J28" t="n">
-        <v>49.05439307162275</v>
+        <v>2.29</v>
       </c>
       <c r="K28" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.52342413113473</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M28" t="n">
-        <v>-409.2008229801629</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.1383758688651809</v>
+        <v>-1.68</v>
       </c>
       <c r="O28" t="n">
-        <v>-433.4672846798917</v>
+        <v>-2.648287934432517</v>
       </c>
       <c r="P28" t="n">
-        <v>-83.76646169972904</v>
+        <v>206.7336965245393</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.0399</v>
+        <v>-2.648287934432743</v>
       </c>
       <c r="R28" t="n">
-        <v>566.6242153201081</v>
+        <v>-2.648287934432517</v>
       </c>
       <c r="S28" t="n">
-        <v>0.09030000000000001</v>
+        <v>-201.3936965245391</v>
       </c>
       <c r="T28" t="n">
-        <v>433.4672846798917</v>
+        <v>-0.0434241311348191</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.138375868865031</v>
+        <v>4.32828793443258</v>
       </c>
       <c r="V28" t="n">
-        <v>-1000</v>
+        <v>2.6482879344326</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.04342413113481911</v>
+        <v>-6.976575868865212</v>
       </c>
       <c r="X28" t="n">
-        <v>0.1383758688651809</v>
+        <v>2.648287934432517</v>
       </c>
       <c r="Y28" t="n">
-        <v>433.4672846798917</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>-433.6056605487571</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.1383758688651809</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-0.138375868865031</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>433.4672846798917</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>-433.4672846798917</v>
+        <v>-2.648287934432517</v>
       </c>
     </row>
     <row r="29">
@@ -3100,91 +2670,76 @@
         <v>25</v>
       </c>
       <c r="B29" t="n">
-        <v>0.02668519213836711</v>
+        <v>0.02668519213836633</v>
       </c>
       <c r="C29" t="n">
         <v>-0.02668519213836711</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.06481480786163286</v>
+        <v>3.05</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.02668519213836711</v>
+        <v>-2.656657403930819</v>
       </c>
       <c r="G29" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.656657403930813</v>
       </c>
       <c r="H29" t="n">
-        <v>419.260180511032</v>
+        <v>-0.02668519213836633</v>
       </c>
       <c r="I29" t="n">
-        <v>458.1602641700759</v>
+        <v>5.989972211792407</v>
       </c>
       <c r="J29" t="n">
-        <v>49.06540553148749</v>
+        <v>2.29</v>
       </c>
       <c r="K29" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.50668519213825</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>-409.2100734464493</v>
+        <v>-59.49999999999993</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.1551148078616329</v>
+        <v>-1.68</v>
       </c>
       <c r="O29" t="n">
-        <v>-433.461117702367</v>
+        <v>-2.656657403930732</v>
       </c>
       <c r="P29" t="n">
-        <v>-83.75104425591714</v>
+        <v>206.6667407685534</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.0399</v>
+        <v>-2.656657403931004</v>
       </c>
       <c r="R29" t="n">
-        <v>566.6303822976331</v>
+        <v>-2.656657403930732</v>
       </c>
       <c r="S29" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.3267407685532</v>
       </c>
       <c r="T29" t="n">
-        <v>433.461117702367</v>
+        <v>-0.02668519213836633</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.155114807861905</v>
+        <v>4.336657403930818</v>
       </c>
       <c r="V29" t="n">
-        <v>-1000</v>
+        <v>2.656657403930813</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.02668519213836711</v>
+        <v>-6.993314807861678</v>
       </c>
       <c r="X29" t="n">
-        <v>0.1551148078616329</v>
+        <v>2.656657403930732</v>
       </c>
       <c r="Y29" t="n">
-        <v>433.461117702367</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>-433.6162325102285</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.1551148078616329</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-0.155114807861905</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>433.461117702367</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>-433.461117702367</v>
+        <v>-2.656657403930732</v>
       </c>
     </row>
     <row r="30">
@@ -3192,91 +2747,76 @@
         <v>26</v>
       </c>
       <c r="B30" t="n">
-        <v>0.004982429915535518</v>
+        <v>0.004982429915534742</v>
       </c>
       <c r="C30" t="n">
         <v>-0.004982429915535518</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.08651757008446448</v>
+        <v>3.05</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.004982429915535518</v>
+        <v>-2.667508785042229</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09029999999999995</v>
+        <v>-2.667508785042234</v>
       </c>
       <c r="H30" t="n">
-        <v>419.2470446286342</v>
+        <v>-0.004982429915534742</v>
       </c>
       <c r="I30" t="n">
-        <v>458.1648331726491</v>
+        <v>6.022526355126651</v>
       </c>
       <c r="J30" t="n">
-        <v>49.07968366452885</v>
+        <v>2.29</v>
       </c>
       <c r="K30" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.48498242991543</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M30" t="n">
-        <v>-409.2220670782044</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.1768175700844644</v>
+        <v>-1.68</v>
       </c>
       <c r="O30" t="n">
-        <v>-433.4531219478638</v>
+        <v>-2.66750878504215</v>
       </c>
       <c r="P30" t="n">
-        <v>-83.73105486965926</v>
+        <v>206.5799297196621</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.0399</v>
+        <v>-2.667508785042415</v>
       </c>
       <c r="R30" t="n">
-        <v>566.6383780521363</v>
+        <v>-2.66750878504215</v>
       </c>
       <c r="S30" t="n">
-        <v>0.09029999999999995</v>
+        <v>-201.2399297196619</v>
       </c>
       <c r="T30" t="n">
-        <v>433.4531219478638</v>
+        <v>-0.004982429915534742</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.1768175700845473</v>
+        <v>4.347508785042229</v>
       </c>
       <c r="V30" t="n">
-        <v>-1000</v>
+        <v>2.667508785042234</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.004982429915535518</v>
+        <v>-7.015017570084503</v>
       </c>
       <c r="X30" t="n">
-        <v>0.1768175700844645</v>
+        <v>2.66750878504215</v>
       </c>
       <c r="Y30" t="n">
-        <v>433.4531219478638</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>-433.6299395179484</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.1768175700844644</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>-0.1768175700845473</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>433.4531219478638</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>-433.4531219478638</v>
+        <v>-2.66750878504215</v>
       </c>
     </row>
     <row r="31">
@@ -3290,85 +2830,70 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G31" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H31" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J31" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K31" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M31" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O31" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P31" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R31" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S31" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T31" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V31" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X31" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y31" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="32">
@@ -3382,85 +2907,70 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G32" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H32" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J32" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K32" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M32" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O32" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P32" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R32" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S32" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T32" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V32" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X32" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y32" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="33">
@@ -3474,85 +2984,70 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G33" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H33" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J33" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K33" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O33" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P33" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R33" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S33" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T33" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V33" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y33" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="34">
@@ -3566,85 +3061,70 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H34" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J34" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K34" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M34" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O34" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P34" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R34" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S34" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T34" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V34" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X34" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y34" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="35">
@@ -3658,85 +3138,70 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G35" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H35" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J35" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K35" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O35" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P35" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R35" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S35" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T35" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V35" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X35" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y35" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="36">
@@ -3750,85 +3215,70 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G36" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H36" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J36" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K36" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M36" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O36" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P36" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R36" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S36" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T36" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V36" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X36" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y36" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="37">
@@ -3842,85 +3292,70 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G37" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H37" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J37" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K37" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M37" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O37" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P37" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R37" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S37" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T37" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V37" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X37" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y37" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="38">
@@ -3934,85 +3369,70 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G38" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H38" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J38" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K38" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M38" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O38" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P38" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R38" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S38" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T38" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V38" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X38" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y38" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="39">
@@ -4026,85 +3446,70 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G39" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H39" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J39" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K39" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M39" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O39" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P39" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R39" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S39" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T39" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V39" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X39" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y39" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="40">
@@ -4118,85 +3523,70 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G40" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H40" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J40" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K40" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M40" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O40" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P40" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R40" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S40" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T40" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V40" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X40" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y40" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="41">
@@ -4210,85 +3600,70 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G41" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H41" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J41" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K41" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M41" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O41" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P41" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R41" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S41" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T41" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V41" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X41" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y41" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="42">
@@ -4302,85 +3677,70 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H42" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J42" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K42" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M42" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O42" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P42" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R42" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S42" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T42" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V42" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X42" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y42" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="43">
@@ -4394,85 +3754,70 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G43" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H43" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J43" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K43" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M43" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O43" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P43" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R43" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S43" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T43" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V43" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X43" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y43" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="44">
@@ -4486,85 +3831,70 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H44" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J44" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K44" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M44" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O44" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P44" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R44" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S44" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T44" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V44" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X44" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y44" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="45">
@@ -4578,85 +3908,70 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G45" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H45" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J45" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K45" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M45" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O45" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P45" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R45" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S45" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T45" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V45" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X45" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y45" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="46">
@@ -4670,85 +3985,70 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G46" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H46" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J46" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K46" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M46" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O46" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P46" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R46" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S46" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T46" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V46" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X46" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y46" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="47">
@@ -4762,85 +4062,70 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G47" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H47" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J47" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K47" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M47" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O47" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P47" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R47" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S47" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T47" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V47" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X47" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y47" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="48">
@@ -4854,85 +4139,70 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H48" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J48" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K48" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M48" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O48" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P48" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R48" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S48" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T48" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V48" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X48" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y48" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="49">
@@ -4946,85 +4216,70 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G49" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H49" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J49" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K49" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M49" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O49" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P49" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R49" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S49" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T49" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V49" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X49" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y49" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="50">
@@ -5038,85 +4293,70 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H50" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J50" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K50" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O50" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P50" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R50" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S50" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T50" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V50" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X50" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y50" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="51">
@@ -5130,85 +4370,70 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G51" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H51" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J51" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K51" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M51" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O51" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P51" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R51" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S51" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T51" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V51" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X51" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y51" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
     <row r="52">
@@ -5222,103 +4447,86 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0915</v>
+        <v>2.29</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0915</v>
+        <v>3.05</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-2.669999999999995</v>
       </c>
       <c r="G52" t="n">
-        <v>0.09029999999999998</v>
+        <v>-2.670000000000003</v>
       </c>
       <c r="H52" t="n">
-        <v>419.2440289473698</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>458.1658821052629</v>
+        <v>6.029999999999951</v>
       </c>
       <c r="J52" t="n">
-        <v>49.0829615789468</v>
+        <v>2.29</v>
       </c>
       <c r="K52" t="n">
-        <v>0.09149999999999998</v>
+        <v>52.47999999999988</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.05039999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="M52" t="n">
-        <v>-409.2248205263156</v>
+        <v>-59.49999999999992</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.1818</v>
+        <v>-1.68</v>
       </c>
       <c r="O52" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="P52" t="n">
-        <v>-83.72646578947399</v>
+        <v>206.5599999999999</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.0399</v>
+        <v>-2.670000000000171</v>
       </c>
       <c r="R52" t="n">
-        <v>566.6402136842105</v>
+        <v>-2.669999999999916</v>
       </c>
       <c r="S52" t="n">
-        <v>0.09029999999999998</v>
+        <v>-201.2199999999997</v>
       </c>
       <c r="T52" t="n">
-        <v>433.4512863157897</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.1818000000002248</v>
+        <v>4.349999999999995</v>
       </c>
       <c r="V52" t="n">
-        <v>-1000</v>
+        <v>2.670000000000003</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>-7.02000000000004</v>
       </c>
       <c r="X52" t="n">
-        <v>0.1818</v>
+        <v>2.669999999999916</v>
       </c>
       <c r="Y52" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>-433.6330863157896</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.1818</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-0.1818000000002248</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>433.4512863157897</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>-433.4512863157897</v>
+        <v>-2.669999999999916</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="AD1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:K1"/>
+  <mergeCells count="12">
+    <mergeCell ref="Y1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="C1"/>
-    <mergeCell ref="D1"/>
-    <mergeCell ref="AB1"/>
-    <mergeCell ref="Z1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="X1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="AA1"/>
-    <mergeCell ref="AC1"/>
+    <mergeCell ref="P1"/>
+    <mergeCell ref="W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
